--- a/hall/resources/sample/MiniGame.xlsx
+++ b/hall/resources/sample/MiniGame.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="24">
   <si>
     <t>sid</t>
   </si>
@@ -107,6 +107,30 @@
   </si>
   <si>
     <t>USDollarExpress</t>
+  </si>
+  <si>
+    <t>空袭</t>
+  </si>
+  <si>
+    <t>AirAttack</t>
+  </si>
+  <si>
+    <t>鸿运扑克</t>
+  </si>
+  <si>
+    <t>LuckyPoker</t>
+  </si>
+  <si>
+    <t>hillo</t>
+  </si>
+  <si>
+    <t>Hillo</t>
+  </si>
+  <si>
+    <t>高低扑克</t>
+  </si>
+  <si>
+    <t>HighLowPoker</t>
   </si>
 </sst>
 </file>
@@ -306,12 +330,12 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -805,7 +829,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -834,17 +858,14 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="60">
@@ -1176,8 +1197,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelRow="4" outlineLevelCol="5"/>
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="3" width="12.6416666666667" style="1" customWidth="1"/>
     <col min="4" max="4" width="11.625" style="1" customWidth="1"/>
@@ -1235,7 +1256,7 @@
       <c r="B3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="10"/>
+      <c r="C3" s="4"/>
       <c r="D3" s="4" t="s">
         <v>10</v>
       </c>
@@ -1246,8 +1267,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="5:5">
-      <c r="E4" s="11" t="s">
+    <row r="4" spans="1:6">
+      <c r="E4" s="1" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1256,19 +1277,99 @@
         <f>B5*100</f>
         <v>100100</v>
       </c>
-      <c r="B5" s="12">
+      <c r="B5" s="10">
         <v>1001</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="13">
+      <c r="D5" s="10">
         <v>50001</v>
       </c>
-      <c r="E5" s="13" t="s">
+      <c r="E5" s="10" t="s">
         <v>15</v>
       </c>
       <c r="F5" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="1">
+        <v>40040000</v>
+      </c>
+      <c r="B6" s="11">
+        <v>400400</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" s="1">
+        <v>400400001</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F6" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="12">
+        <v>40020000</v>
+      </c>
+      <c r="B7" s="12">
+        <v>400200</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" s="1">
+        <v>400200001</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F7" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="12">
+        <v>40050000</v>
+      </c>
+      <c r="B8" s="12">
+        <v>400500</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" s="1">
+        <v>400500001</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F8" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="12">
+        <v>40070000</v>
+      </c>
+      <c r="B9" s="12">
+        <v>400700</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9" s="1">
+        <v>400700001</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F9" s="1">
         <v>0</v>
       </c>
     </row>

--- a/hall/resources/sample/MiniGame.xlsx
+++ b/hall/resources/sample/MiniGame.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="16">
   <si>
     <t>sid</t>
   </si>
@@ -107,30 +107,6 @@
   </si>
   <si>
     <t>USDollarExpress</t>
-  </si>
-  <si>
-    <t>空袭</t>
-  </si>
-  <si>
-    <t>AirAttack</t>
-  </si>
-  <si>
-    <t>鸿运扑克</t>
-  </si>
-  <si>
-    <t>LuckyPoker</t>
-  </si>
-  <si>
-    <t>hillo</t>
-  </si>
-  <si>
-    <t>Hillo</t>
-  </si>
-  <si>
-    <t>高低扑克</t>
-  </si>
-  <si>
-    <t>HighLowPoker</t>
   </si>
 </sst>
 </file>
@@ -1294,84 +1270,23 @@
       </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="1">
-        <v>40040000</v>
-      </c>
-      <c r="B6" s="11">
-        <v>400400</v>
-      </c>
-      <c r="C6" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="D6" s="1">
-        <v>400400001</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F6" s="1">
-        <v>0</v>
-      </c>
+      <c r="B6" s="11"/>
+      <c r="C6" s="11"/>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="12">
-        <v>40020000</v>
-      </c>
-      <c r="B7" s="12">
-        <v>400200</v>
-      </c>
-      <c r="C7" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="D7" s="1">
-        <v>400200001</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F7" s="1">
-        <v>0</v>
-      </c>
+      <c r="A7" s="12"/>
+      <c r="B7" s="12"/>
+      <c r="C7" s="12"/>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="12">
-        <v>40050000</v>
-      </c>
-      <c r="B8" s="12">
-        <v>400500</v>
-      </c>
-      <c r="C8" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="D8" s="1">
-        <v>400500001</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F8" s="1">
-        <v>0</v>
-      </c>
+      <c r="A8" s="12"/>
+      <c r="B8" s="12"/>
+      <c r="C8" s="12"/>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="12">
-        <v>40070000</v>
-      </c>
-      <c r="B9" s="12">
-        <v>400700</v>
-      </c>
-      <c r="C9" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="D9" s="1">
-        <v>400700001</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F9" s="1">
-        <v>0</v>
-      </c>
+      <c r="A9" s="12"/>
+      <c r="B9" s="12"/>
+      <c r="C9" s="12"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
